--- a/docs/downloads/11/tbl_degats_champs_riz_alaotra_mangabe.xlsx
+++ b/docs/downloads/11/tbl_degats_champs_riz_alaotra_mangabe.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -418,20 +418,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="4">
@@ -442,17 +442,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grêle</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -466,41 +466,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C5">
-        <v>50</v>
+        <v>53.1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
-        <v>33.3</v>
+        <v>22.4</v>
       </c>
       <c r="F5">
-        <v>16.7</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Maladie</t>
+          <t>Autres</t>
         </is>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -509,49 +509,49 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rats</t>
+          <t>Autres bestioles</t>
         </is>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="D7">
-        <v>37.5</v>
+        <v>71.2</v>
       </c>
       <c r="E7">
-        <v>62.5</v>
+        <v>13.5</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Tous</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sécheresse</t>
+          <t>Cyclone</t>
         </is>
       </c>
       <c r="C8">
-        <v>53.1</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>22.4</v>
+        <v>70</v>
       </c>
       <c r="F8">
-        <v>22.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -562,17 +562,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Facteur humain</t>
         </is>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>94.3</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>2.9</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -586,20 +586,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Autres bestioles</t>
+          <t>Grêle</t>
         </is>
       </c>
       <c r="C10">
-        <v>13.5</v>
+        <v>77.8</v>
       </c>
       <c r="D10">
-        <v>71.2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>13.5</v>
+        <v>22.2</v>
       </c>
       <c r="F10">
-        <v>1.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -610,20 +610,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cyclone</t>
+          <t>Inondation</t>
         </is>
       </c>
       <c r="C11">
-        <v>20</v>
+        <v>46.2</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>2.6</v>
       </c>
       <c r="E11">
-        <v>70</v>
+        <v>43.6</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="12">
@@ -634,17 +634,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Facteur humain</t>
+          <t>Maladie</t>
         </is>
       </c>
       <c r="C12">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D12">
-        <v>94.3</v>
+        <v>87.5</v>
       </c>
       <c r="E12">
-        <v>2.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -658,17 +658,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grêle</t>
+          <t>Rats</t>
         </is>
       </c>
       <c r="C13">
-        <v>77.8</v>
+        <v>12.2</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>29.3</v>
       </c>
       <c r="E13">
-        <v>22.2</v>
+        <v>58.5</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -682,91 +682,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Inondation</t>
+          <t>Sécheresse</t>
         </is>
       </c>
       <c r="C14">
-        <v>46.2</v>
+        <v>58.6</v>
       </c>
       <c r="D14">
-        <v>2.6</v>
+        <v>5.4</v>
       </c>
       <c r="E14">
-        <v>43.6</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>7.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Maladie</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>4.2</v>
-      </c>
-      <c r="D15">
-        <v>87.5</v>
-      </c>
-      <c r="E15">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rats</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>12.2</v>
-      </c>
-      <c r="D16">
-        <v>29.3</v>
-      </c>
-      <c r="E16">
-        <v>58.5</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Alaotra - Tous</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Sécheresse</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>58.6</v>
-      </c>
-      <c r="D17">
-        <v>5.4</v>
-      </c>
-      <c r="E17">
-        <v>23</v>
-      </c>
-      <c r="F17">
         <v>13.1</v>
       </c>
     </row>
